--- a/Data/Export/Common/TerrainType_地形类型.xlsx
+++ b/Data/Export/Common/TerrainType_地形类型.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="148">
   <si>
     <t>0</t>
   </si>
@@ -564,6 +564,18 @@
   <si>
     <t>i8</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远海</t>
+  </si>
+  <si>
+    <t>48,86,130</t>
+  </si>
+  <si>
+    <t>深海</t>
+  </si>
+  <si>
+    <t>28,56,96</t>
   </si>
 </sst>
 </file>
@@ -2513,7 +2525,7 @@
         <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>118</v>
@@ -2543,10 +2555,10 @@
         <v>3</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>3</v>
@@ -2558,7 +2570,7 @@
         <v>95</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="T26" s="4"/>
       <c r="V26" s="4"/>
@@ -2571,7 +2583,7 @@
         <v>22</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>46</v>
+        <v>146</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>118</v>
@@ -2601,10 +2613,10 @@
         <v>3</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>3</v>
@@ -2616,7 +2628,7 @@
         <v>95</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="T27" s="4"/>
       <c r="V27" s="4"/>
